--- a/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por revisión o chequeo</t>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,06; 71,51</t>
+          <t>52,87; 70,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,35; 83,67</t>
+          <t>66,35; 83,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,21; 75,56</t>
+          <t>56,71; 75,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71,2; 88,29</t>
+          <t>71,29; 87,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,96; 78,62</t>
+          <t>61,58; 78,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,38; 75,26</t>
+          <t>55,97; 73,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,92; 86,57</t>
+          <t>71,42; 86,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,57; 92,72</t>
+          <t>76,04; 93,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,57; 72,21</t>
+          <t>60,05; 72,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,19; 76,42</t>
+          <t>64,81; 76,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,45; 79,77</t>
+          <t>67,26; 79,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,2; 89,09</t>
+          <t>77,18; 89,19</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,47; 74,37</t>
+          <t>60,08; 73,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,58; 71,34</t>
+          <t>56,91; 71,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,14; 76,47</t>
+          <t>62,3; 76,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,15; 91,86</t>
+          <t>79,93; 91,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,71; 78,85</t>
+          <t>65,32; 79,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,04; 84,4</t>
+          <t>72,24; 84,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,65; 78,6</t>
+          <t>64,44; 78,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,23; 84,22</t>
+          <t>71,92; 84,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,2; 74,88</t>
+          <t>64,91; 74,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,82; 76,1</t>
+          <t>66,78; 76,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,87; 75,07</t>
+          <t>65,99; 75,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,35; 86,48</t>
+          <t>77,19; 86,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,71; 78,8</t>
+          <t>62,96; 79,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,69; 82,24</t>
+          <t>66,51; 81,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,11; 85,26</t>
+          <t>69,64; 84,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,95; 79,74</t>
+          <t>62,59; 79,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,8; 80,51</t>
+          <t>64,0; 79,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,99; 79,53</t>
+          <t>63,09; 79,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,25; 79,08</t>
+          <t>63,19; 79,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,84; 87,22</t>
+          <t>72,22; 86,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,69; 78,41</t>
+          <t>66,73; 77,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,59; 79,0</t>
+          <t>67,51; 79,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 80,12</t>
+          <t>68,93; 80,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,14; 81,5</t>
+          <t>69,27; 80,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,39; 72,22</t>
+          <t>54,64; 71,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,56; 83,63</t>
+          <t>67,35; 82,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,99; 84,63</t>
+          <t>72,21; 84,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,35; 91,86</t>
+          <t>80,65; 91,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,67; 77,31</t>
+          <t>60,87; 76,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,01; 89,66</t>
+          <t>75,83; 89,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,24; 85,5</t>
+          <t>72,43; 85,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,96; 92,5</t>
+          <t>80,25; 92,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,18; 71,39</t>
+          <t>59,73; 72,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,71; 84,65</t>
+          <t>74,57; 84,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,96; 83,51</t>
+          <t>74,06; 83,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,89; 91,18</t>
+          <t>82,65; 91,15</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,4; 69,76</t>
+          <t>61,94; 69,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,86; 75,75</t>
+          <t>68,27; 75,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,6; 77,51</t>
+          <t>69,4; 77,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,96; 84,91</t>
+          <t>78,06; 85,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,59; 75,19</t>
+          <t>67,68; 75,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 79,4</t>
+          <t>72,12; 79,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,68</t>
+          <t>72,03; 79,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,69</t>
+          <t>78,33; 85,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,89; 71,63</t>
+          <t>65,98; 71,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,46; 76,69</t>
+          <t>71,36; 76,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,09; 77,36</t>
+          <t>71,97; 77,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,54</t>
+          <t>79,27; 84,32</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>47353</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56853</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47394</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56586</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57894</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50274</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61892</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>73625</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>105247</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>107128</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>109286</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>130212</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>40009; 53466</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50036; 62855</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40175; 53693</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49733; 61343</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>50611; 64374</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>42545; 56153</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>55217; 67091</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>64828; 79546</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>94795; 114410</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>98149; 116349</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>99643; 117914</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>119639; 138262</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>74485</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72811</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75244</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98574</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81141</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90670</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78290</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>131887</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>155626</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>163482</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>153535</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>230460</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>66122; 81112</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>64080; 80556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67264; 82419</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>90905; 104233</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>72914; 88421</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>83311; 97264</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>69977; 85204</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>120371; 140936</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>143897; 165482</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>152202; 174522</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>142905; 164076</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>217001; 242212</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>49486</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56335</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59010</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76419</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56876</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57501</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56288</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>96507</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>106362</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113836</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>172926</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>43573; 54951</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49904; 61522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52637; 63769</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>66943; 85503</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>49839; 61818</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>50316; 63193</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>49381; 62022</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>86843; 104403</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>98145; 114457</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>104501; 122352</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>105966; 123720</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>157379; 184021</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>60895</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70793</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86919</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>88287</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62309</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80687</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85503</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>97252</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>123203</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151479</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>172422</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>185541</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>52448; 68182</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62620; 77138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79891; 94003</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81606; 93010</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>54810; 68735</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>73029; 86278</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>77755; 91683</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>89533; 103044</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>111112; 134130</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>141153; 160340</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>161433; 182252</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>175832; 193931</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>232218</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>256792</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>268568</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>319866</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>399272</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>490437</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535924</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>550541</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>719137</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>217367; 245325</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>243057; 269024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>253328; 282120</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>305727; 332886</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>244823; 271292</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>264985; 292453</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>267518; 294469</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>379470; 414420</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>470225; 511548</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>516222; 555101</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>529969; 569772</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>694445; 738683</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,87; 70,65</t>
+          <t>52,72; 70,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,35; 83,35</t>
+          <t>65,69; 83,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,71; 75,79</t>
+          <t>56,01; 74,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71,29; 87,93</t>
+          <t>71,69; 88,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,58; 78,33</t>
+          <t>61,72; 77,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,97; 73,87</t>
+          <t>55,89; 74,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,42; 86,78</t>
+          <t>70,96; 86,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,04; 93,31</t>
+          <t>76,46; 92,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,05; 72,47</t>
+          <t>60,09; 72,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,81; 76,83</t>
+          <t>64,22; 76,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,26; 79,59</t>
+          <t>67,01; 79,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,18; 89,19</t>
+          <t>77,84; 89,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,08; 73,7</t>
+          <t>61,06; 74,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,91; 71,54</t>
+          <t>58,01; 71,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,3; 76,34</t>
+          <t>62,3; 76,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,93; 91,65</t>
+          <t>79,96; 91,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,32; 79,21</t>
+          <t>66,08; 78,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,24; 84,34</t>
+          <t>72,34; 84,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,44; 78,46</t>
+          <t>64,97; 78,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,92; 84,2</t>
+          <t>71,65; 83,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,91; 74,65</t>
+          <t>65,27; 74,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,78; 76,57</t>
+          <t>66,8; 76,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65,99; 75,77</t>
+          <t>66,18; 75,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,19; 86,16</t>
+          <t>76,81; 85,56</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,96; 79,4</t>
+          <t>62,11; 78,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,51; 81,99</t>
+          <t>66,61; 82,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,64; 84,36</t>
+          <t>69,2; 84,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,59; 79,94</t>
+          <t>61,54; 79,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,0; 79,39</t>
+          <t>64,43; 80,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,09; 79,24</t>
+          <t>63,54; 79,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,19; 79,36</t>
+          <t>62,99; 79,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,22; 86,82</t>
+          <t>71,19; 86,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,73; 77,82</t>
+          <t>66,07; 77,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,51; 79,05</t>
+          <t>67,64; 79,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,93; 80,48</t>
+          <t>69,08; 80,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,27; 80,99</t>
+          <t>69,6; 81,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,64; 71,03</t>
+          <t>54,03; 71,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,35; 82,97</t>
+          <t>67,1; 83,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,21; 84,97</t>
+          <t>70,58; 84,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,65; 91,93</t>
+          <t>80,39; 92,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,87; 76,34</t>
+          <t>60,55; 76,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,83; 89,59</t>
+          <t>76,86; 89,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 85,41</t>
+          <t>72,41; 85,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,25; 92,36</t>
+          <t>79,58; 92,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,73; 72,1</t>
+          <t>59,72; 70,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,57; 84,71</t>
+          <t>74,58; 85,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,06; 83,61</t>
+          <t>74,75; 83,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,65; 91,15</t>
+          <t>82,46; 90,99</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,94; 69,91</t>
+          <t>61,72; 69,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,27; 75,56</t>
+          <t>68,27; 76,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,29</t>
+          <t>69,72; 77,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78,06; 85,0</t>
+          <t>77,71; 84,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,68; 75,0</t>
+          <t>67,62; 74,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,12; 79,6</t>
+          <t>72,1; 79,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,03; 79,29</t>
+          <t>72,19; 79,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,33; 85,55</t>
+          <t>78,68; 85,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65,98; 71,78</t>
+          <t>66,07; 71,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,73</t>
+          <t>71,43; 76,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 77,37</t>
+          <t>72,01; 77,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,27; 84,32</t>
+          <t>79,53; 84,44</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40009; 53466</t>
+          <t>39894; 53703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50036; 62855</t>
+          <t>49534; 62780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40175; 53693</t>
+          <t>39677; 52860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49733; 61343</t>
+          <t>50012; 61800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50611; 64374</t>
+          <t>50727; 63897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42545; 56153</t>
+          <t>42489; 56636</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55217; 67091</t>
+          <t>54860; 67225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64828; 79546</t>
+          <t>65180; 79101</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94795; 114410</t>
+          <t>94857; 114596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>98149; 116349</t>
+          <t>97254; 116313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99643; 117914</t>
+          <t>99279; 117480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>119639; 138262</t>
+          <t>120659; 139066</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66122; 81112</t>
+          <t>67198; 82165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64080; 80556</t>
+          <t>65322; 80490</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67264; 82419</t>
+          <t>67262; 82280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90905; 104233</t>
+          <t>90938; 104009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72914; 88421</t>
+          <t>73762; 87888</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83311; 97264</t>
+          <t>83426; 97166</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69977; 85204</t>
+          <t>70552; 85553</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>120371; 140936</t>
+          <t>119924; 140475</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>143897; 165482</t>
+          <t>144694; 165469</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152202; 174522</t>
+          <t>152259; 174095</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142905; 164076</t>
+          <t>143319; 163701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>217001; 242212</t>
+          <t>215931; 240512</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43573; 54951</t>
+          <t>42984; 54447</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49904; 61522</t>
+          <t>49981; 62081</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52637; 63769</t>
+          <t>52305; 64172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66943; 85503</t>
+          <t>65824; 84802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49839; 61818</t>
+          <t>50174; 62388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50316; 63193</t>
+          <t>50678; 63380</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49381; 62022</t>
+          <t>49230; 62411</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86843; 104403</t>
+          <t>85605; 104002</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98145; 114457</t>
+          <t>97178; 114026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104501; 122352</t>
+          <t>104700; 122661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>105966; 123720</t>
+          <t>106203; 124074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>157379; 184021</t>
+          <t>158128; 184233</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52448; 68182</t>
+          <t>51858; 68882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62620; 77138</t>
+          <t>62387; 77459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79891; 94003</t>
+          <t>78086; 93968</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81606; 93010</t>
+          <t>81333; 93080</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54810; 68735</t>
+          <t>54520; 69304</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73029; 86278</t>
+          <t>74016; 86135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77755; 91683</t>
+          <t>77732; 91803</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89533; 103044</t>
+          <t>88784; 102976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111112; 134130</t>
+          <t>111094; 132020</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>141153; 160340</t>
+          <t>141169; 161445</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161433; 182252</t>
+          <t>162941; 182661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>175832; 193931</t>
+          <t>175435; 193582</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>217367; 245325</t>
+          <t>216587; 244928</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>243057; 269024</t>
+          <t>243040; 270963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253328; 282120</t>
+          <t>254511; 283010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>305727; 332886</t>
+          <t>304341; 332207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>244823; 271292</t>
+          <t>244598; 271064</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264985; 292453</t>
+          <t>264906; 292529</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>267518; 294469</t>
+          <t>268115; 294193</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>379470; 414420</t>
+          <t>381145; 414784</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>470225; 511548</t>
+          <t>470844; 509320</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>516222; 555101</t>
+          <t>516752; 553917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>529969; 569772</t>
+          <t>530285; 568634</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>694445; 738683</t>
+          <t>696742; 739765</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80,06%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>62,58%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>75,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>66,9%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81,11%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,06%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,72; 70,97</t>
+          <t>61,96; 78,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,25</t>
+          <t>57,38; 75,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,01; 74,62</t>
+          <t>70,92; 86,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71,69; 88,58</t>
+          <t>77,66; 93,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,72; 77,74</t>
+          <t>53,06; 71,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,89; 74,5</t>
+          <t>66,35; 83,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,96; 86,96</t>
+          <t>56,21; 75,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76,46; 92,79</t>
+          <t>71,41; 88,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,09; 72,59</t>
+          <t>59,57; 72,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,22; 76,81</t>
+          <t>64,19; 76,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,01; 79,3</t>
+          <t>67,45; 79,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,84; 89,71</t>
+          <t>77,9; 89,11</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>67,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>64,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>69,7%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>72,69%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>78,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,06; 74,65</t>
+          <t>65,71; 78,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,01; 71,48</t>
+          <t>72,04; 84,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,3; 76,21</t>
+          <t>64,65; 78,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,96; 91,45</t>
+          <t>72,09; 84,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,08; 78,73</t>
+          <t>60,47; 74,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,34; 84,26</t>
+          <t>56,58; 71,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,97; 78,78</t>
+          <t>62,14; 76,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,65; 83,93</t>
+          <t>79,26; 91,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,27; 74,64</t>
+          <t>65,2; 74,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,8; 76,38</t>
+          <t>66,82; 76,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66,18; 75,59</t>
+          <t>64,87; 75,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,81; 85,56</t>
+          <t>77,32; 86,42</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79,33%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>75,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>78,07%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,11; 78,67</t>
+          <t>64,8; 80,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,61; 82,74</t>
+          <t>62,99; 79,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,2; 84,9</t>
+          <t>63,25; 79,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,54; 79,29</t>
+          <t>69,69; 86,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,43; 80,12</t>
+          <t>62,71; 78,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,54; 79,47</t>
+          <t>65,69; 82,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,99; 79,86</t>
+          <t>70,11; 85,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,19; 86,49</t>
+          <t>63,74; 79,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,07; 77,53</t>
+          <t>66,69; 78,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,64; 79,24</t>
+          <t>67,59; 79,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,08; 80,71</t>
+          <t>69,42; 80,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,6; 81,09</t>
+          <t>69,89; 81,12</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>69,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>63,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>76,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>78,56%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>69,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,03; 71,76</t>
+          <t>60,67; 77,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,1; 83,31</t>
+          <t>78,01; 89,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,58; 84,94</t>
+          <t>72,24; 85,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,39; 92,0</t>
+          <t>80,78; 92,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,55; 76,97</t>
+          <t>54,39; 72,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,86; 89,44</t>
+          <t>67,56; 83,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,41; 85,52</t>
+          <t>70,99; 84,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 92,3</t>
+          <t>79,72; 91,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,72; 70,97</t>
+          <t>60,18; 71,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,58; 85,3</t>
+          <t>74,71; 84,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,75; 83,8</t>
+          <t>73,96; 83,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,46; 90,99</t>
+          <t>83,45; 91,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,72; 69,79</t>
+          <t>67,59; 75,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,27; 76,11</t>
+          <t>71,97; 79,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,72; 77,53</t>
+          <t>72,19; 79,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,71; 84,83</t>
+          <t>78,56; 85,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,62; 74,94</t>
+          <t>61,4; 69,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,1; 79,62</t>
+          <t>67,86; 75,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,21</t>
+          <t>69,6; 77,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,68; 85,62</t>
+          <t>78,44; 85,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,07; 71,47</t>
+          <t>65,89; 71,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,43; 76,57</t>
+          <t>71,46; 76,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,22</t>
+          <t>72,09; 77,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,53; 84,44</t>
+          <t>79,84; 84,58</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57894</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50274</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61892</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>70905</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>47353</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>56853</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>47394</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56586</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>57894</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50274</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61892</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>131226</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39894; 53703</t>
+          <t>50923; 64615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49534; 62780</t>
+          <t>43621; 57211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39677; 52860</t>
+          <t>54830; 66930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50012; 61800</t>
+          <t>63261; 75825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50727; 63897</t>
+          <t>40154; 54111</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42489; 56636</t>
+          <t>50036; 63095</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54860; 67225</t>
+          <t>39821; 53527</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65180; 79101</t>
+          <t>53040; 65655</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94857; 114596</t>
+          <t>94036; 113994</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97254; 116313</t>
+          <t>97208; 115729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99279; 117480</t>
+          <t>99932; 118185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>120659; 139066</t>
+          <t>121316; 138771</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>143</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78290</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>128289</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>74485</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>72811</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>75244</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>98574</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81141</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90670</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78290</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>131887</t>
+          <t>101067</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>230460</t>
+          <t>229355</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67198; 82165</t>
+          <t>73352; 88019</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65322; 80490</t>
+          <t>83076; 97336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67262; 82280</t>
+          <t>70199; 85358</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90938; 104009</t>
+          <t>117024; 136929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>73762; 87888</t>
+          <t>66550; 81851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83426; 97166</t>
+          <t>63713; 80328</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70552; 85553</t>
+          <t>67089; 82557</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119924; 140475</t>
+          <t>92723; 107008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>144694; 165469</t>
+          <t>144541; 166008</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152259; 174095</t>
+          <t>152302; 173441</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143319; 163701</t>
+          <t>140488; 162565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>215931; 240512</t>
+          <t>215968; 241378</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56876</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57501</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56288</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88925</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>49486</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>56335</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>59010</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76419</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56876</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57501</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56288</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>73522</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>162448</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42984; 54447</t>
+          <t>50456; 62696</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49981; 62081</t>
+          <t>50237; 63426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52305; 64172</t>
+          <t>49430; 61803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65824; 84802</t>
+          <t>78122; 97197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50174; 62388</t>
+          <t>43397; 54539</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50678; 63380</t>
+          <t>49292; 61710</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49230; 62411</t>
+          <t>52997; 64447</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85605; 104002</t>
+          <t>65297; 81193</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97178; 114026</t>
+          <t>98080; 115321</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104700; 122661</t>
+          <t>104620; 122289</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106203; 124074</t>
+          <t>106723; 123167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>158128; 184233</t>
+          <t>149949; 174032</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>114</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80687</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85503</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92538</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>60895</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>70793</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>86919</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>88287</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62309</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80687</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85503</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>89500</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>185541</t>
+          <t>182038</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51858; 68882</t>
+          <t>54632; 69615</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62387; 77459</t>
+          <t>75120; 86345</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78086; 93968</t>
+          <t>77555; 91782</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81333; 93080</t>
+          <t>84990; 97416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54520; 69304</t>
+          <t>52207; 69328</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74016; 86135</t>
+          <t>62811; 77755</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77732; 91803</t>
+          <t>78539; 93626</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88784; 102976</t>
+          <t>81771; 94156</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111094; 132020</t>
+          <t>111958; 132812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>141169; 161445</t>
+          <t>141405; 160230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162941; 182661</t>
+          <t>161214; 182040</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>175435; 193582</t>
+          <t>173404; 189339</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>386</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>460</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>216587; 244928</t>
+          <t>244477; 272001</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>243040; 270963</t>
+          <t>264423; 291726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>254511; 283010</t>
+          <t>268126; 295931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304341; 332207</t>
+          <t>362215; 394644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>244598; 271064</t>
+          <t>215484; 244818</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264906; 292529</t>
+          <t>241589; 269703</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>268115; 294193</t>
+          <t>254062; 282940</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>381145; 414784</t>
+          <t>310839; 337298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>470844; 509320</t>
+          <t>469582; 510472</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>516752; 553917</t>
+          <t>516958; 554768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>530285; 568634</t>
+          <t>530895; 569710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>696742; 739765</t>
+          <t>684521; 725196</t>
         </is>
       </c>
     </row>
